--- a/downloads/samples/Opportunities_SAMPLE.xlsx
+++ b/downloads/samples/Opportunities_SAMPLE.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -486,9 +486,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="52" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -546,16 +544,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Last used</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
           <t>Missing Info</t>
         </is>
       </c>
@@ -606,13 +594,7 @@
           <t>https://example.edu/climate-venture-studio</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="39" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -660,13 +642,7 @@
           <t>https://example.gov/pcef-grants</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr"/>
-      <c r="L4" s="4" t="inlineStr"/>
+      <c r="J4" s="4" t="inlineStr"/>
     </row>
     <row r="5" ht="39" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
@@ -714,13 +690,7 @@
           <t>https://example.org/oregon-best-grant</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
     </row>
     <row r="6" ht="39" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
@@ -768,13 +738,7 @@
           <t>https://example.org/storytelling-call</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr"/>
     </row>
     <row r="7" ht="39" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -822,13 +786,7 @@
           <t>https://example.org/energy-trust-pilot</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr"/>
-      <c r="L7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
     </row>
     <row r="8" ht="39" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -876,13 +834,7 @@
           <t>https://example.org/wac</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr"/>
-      <c r="L8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr"/>
     </row>
     <row r="9" ht="39" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -930,13 +882,7 @@
           <t>https://example.org/cascadia-accelerator</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr"/>
     </row>
     <row r="10" ht="39" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
@@ -984,13 +930,7 @@
           <t>https://example.org/nextgen-fellowship</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
+      <c r="J10" s="3" t="inlineStr"/>
     </row>
     <row r="11" ht="39" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
@@ -1038,13 +978,7 @@
           <t>https://example.gov/doe-sbir</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr"/>
-      <c r="L11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr"/>
     </row>
     <row r="12" ht="39" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
@@ -1092,13 +1026,7 @@
           <t>https://example.org/activate</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr"/>
-      <c r="L12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr"/>
     </row>
     <row r="13" ht="39" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
@@ -1146,13 +1074,7 @@
           <t>https://example.gov/epa-ej</t>
         </is>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr"/>
-      <c r="L13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr"/>
     </row>
     <row r="14" ht="39" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
@@ -1200,13 +1122,7 @@
           <t>https://example.org/elemental</t>
         </is>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr"/>
-      <c r="L14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr"/>
     </row>
     <row r="15" ht="39" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -1254,13 +1170,7 @@
           <t>https://example.org/greentown</t>
         </is>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr"/>
-      <c r="L15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
     </row>
     <row r="16" ht="39" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
@@ -1308,13 +1218,7 @@
           <t>https://example.gov/arpa-e-open</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
+      <c r="J16" s="3" t="inlineStr"/>
     </row>
     <row r="17" ht="39" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
@@ -1362,13 +1266,7 @@
           <t>https://example.org/be-fellows</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="inlineStr"/>
-      <c r="L17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
     </row>
     <row r="18" ht="39" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
@@ -1416,17 +1314,11 @@
           <t>https://example.org/third-derivative</t>
         </is>
       </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>Not used</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="inlineStr"/>
-      <c r="L18" s="4" t="inlineStr"/>
+      <c r="J18" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
